--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487174_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487174_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. KEITH CAMARA</t>
+          <t>J. OTERO GONZALEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1243</v>
+        <v>1.1265</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6476</v>
+        <v>4.1943</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5233</v>
+        <v>-3.0678</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3083</v>
+        <v>-0.3202</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.416</v>
+        <v>0.121</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7243</v>
+        <v>-0.4413</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4413</v>
+        <v>1.6419</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0983</v>
+        <v>1.6505</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3431</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.133</v>
+        <v>-1.9622</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5143</v>
+        <v>-1.5295</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3813</v>
+        <v>-0.4327</v>
       </c>
       <c r="P2" t="n">
-        <v>0.772</v>
+        <v>1.5441</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.193</v>
+        <v>-0.386</v>
       </c>
       <c r="R2" t="n">
-        <v>0.965</v>
+        <v>1.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0562</v>
+        <v>-1.0394</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3993</v>
+        <v>-0.7456</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4554</v>
+        <v>-0.2938</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.8999</v>
+        <v>0.9421</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.6839</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8999</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. OTERO GONZALEZ</t>
+          <t>D. KEITH CAMARA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4136</v>
+        <v>0.8507</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6152</v>
+        <v>1.3472</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.2016</v>
+        <v>-0.4965</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3202</v>
+        <v>1.3083</v>
       </c>
       <c r="H3" t="n">
-        <v>0.121</v>
+        <v>-0.416</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4413</v>
+        <v>1.7243</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6419</v>
+        <v>1.4413</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6505</v>
+        <v>0.0983</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.008500000000000001</v>
+        <v>1.3431</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9622</v>
+        <v>-0.133</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5295</v>
+        <v>-0.5143</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4327</v>
+        <v>0.3813</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5441</v>
+        <v>0.772</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.386</v>
+        <v>-0.193</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9301</v>
+        <v>0.965</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7523</v>
+        <v>-0.3298</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3246</v>
+        <v>0.0988</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4277</v>
+        <v>-0.4287</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9421</v>
+        <v>-0.8999</v>
       </c>
       <c r="W3" t="n">
-        <v>3.6839</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.7418</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4489</v>
+        <v>-0.0622</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6254</v>
+        <v>1.5035</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0743</v>
+        <v>-1.5657</v>
       </c>
       <c r="G4" t="n">
         <v>1.6193</v>
@@ -766,13 +766,13 @@
         <v>1.5441</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4892</v>
+        <v>-1.1025</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3595</v>
+        <v>-0.4815</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1296</v>
+        <v>-0.621</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. CARPINTERO REVILLA</t>
+          <t>O. HERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5497</v>
+        <v>-0.9621</v>
       </c>
       <c r="E5" t="n">
-        <v>0.078</v>
+        <v>0.4346</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6277</v>
+        <v>-1.3967</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6062</v>
+        <v>-0.2576</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4509</v>
+        <v>-1.1273</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8447</v>
+        <v>0.8697</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5334</v>
+        <v>-0.959</v>
       </c>
       <c r="K5" t="n">
-        <v>3.0789</v>
+        <v>-1.0404</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5455</v>
+        <v>0.0814</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9272</v>
+        <v>0.7014</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.628</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2992</v>
+        <v>0.7883</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0.579</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3511</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2717</v>
+        <v>-0.0555</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4481</v>
+        <v>0.1656</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1764</v>
+        <v>-0.2211</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8842</v>
+        <v>-1.228</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6562</v>
+        <v>1.228</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.228</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. HERNANDEZ HERNANDEZ</t>
+          <t>E. CARPINTERO REVILLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0553</v>
+        <v>-1.1862</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4752</v>
+        <v>-0.1034</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5305</v>
+        <v>-1.0828</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2576</v>
+        <v>1.6062</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1273</v>
+        <v>2.4509</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8697</v>
+        <v>-0.8447</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.959</v>
+        <v>2.5334</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.0404</v>
+        <v>3.0789</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0814</v>
+        <v>-0.5455</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7014</v>
+        <v>-0.9272</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.628</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7883</v>
+        <v>-0.2992</v>
       </c>
       <c r="P6" t="n">
-        <v>0.579</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.3511</v>
       </c>
       <c r="R6" t="n">
-        <v>0.579</v>
+        <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1487</v>
+        <v>-0.9082</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2062</v>
+        <v>-0.6296</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.355</v>
+        <v>-0.2786</v>
       </c>
       <c r="V6" t="n">
+        <v>-1.8842</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.6562</v>
+      </c>
+      <c r="X6" t="n">
         <v>-1.228</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.228</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-2.4559</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. NDOYE</t>
+          <t>A. REYES ABAD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0587</v>
+        <v>-1.4445</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1384</v>
+        <v>-0.731</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07969999999999999</v>
+        <v>-0.7134</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8275</v>
+        <v>-2.773</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7346</v>
+        <v>-0.8516</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-1.9214</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6321</v>
+        <v>-1.5182</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0052</v>
+        <v>0.5175</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6269</v>
+        <v>-2.0356</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1953</v>
+        <v>-1.2549</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7294</v>
+        <v>-1.3691</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5341</v>
+        <v>0.1142</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.386</v>
+        <v>1.5441</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.965</v>
+        <v>-0.193</v>
       </c>
       <c r="R7" t="n">
-        <v>0.579</v>
+        <v>1.7371</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1547</v>
+        <v>-0.5014</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4587</v>
+        <v>-0.5337</v>
       </c>
       <c r="U7" t="n">
-        <v>0.696</v>
+        <v>0.0324</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. REYES ABAD</t>
+          <t>A. REY GUTIERREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6556</v>
+        <v>-1.6992</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2099</v>
+        <v>-0.8423</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4457</v>
+        <v>-0.8568</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.773</v>
+        <v>-0.86</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8516</v>
+        <v>-0.9936</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.9214</v>
+        <v>0.1335</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5182</v>
+        <v>0.0414</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5175</v>
+        <v>0.0414</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0356</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2549</v>
+        <v>-0.9014</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3691</v>
+        <v>-1.035</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1142</v>
+        <v>0.1335</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5441</v>
+        <v>-0.965</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.193</v>
+        <v>-0.965</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7371</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7125</v>
+        <v>0.1259</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0126</v>
+        <v>0.0813</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3001</v>
+        <v>0.0446</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. REY GUTIERREZ</t>
+          <t>N. NDOYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9262</v>
+        <v>-1.7537</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0426</v>
+        <v>-1.539</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-0.2148</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.86</v>
+        <v>-1.8275</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9936</v>
+        <v>-1.7346</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1335</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0414</v>
+        <v>-0.6321</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0414</v>
+        <v>-0.0052</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.6269</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9014</v>
+        <v>-1.1953</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.035</v>
+        <v>-1.7294</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1335</v>
+        <v>0.5341</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.965</v>
+        <v>-0.386</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.965</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1011</v>
+        <v>0.4597</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.119</v>
+        <v>0.0582</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0178</v>
+        <v>0.4015</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7001</v>
+        <v>-2.4195</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.532</v>
+        <v>-2.3317</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1681</v>
+        <v>-0.0877</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3546</v>
@@ -1234,13 +1234,13 @@
         <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8666</v>
+        <v>-0.586</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5063</v>
+        <v>-0.306</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3603</v>
+        <v>-0.28</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2859</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9462</v>
+        <v>-4.3602</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7881</v>
+        <v>-3.3092</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1581</v>
+        <v>-1.051</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6159</v>
@@ -1312,13 +1312,13 @@
         <v>1.9301</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8442</v>
+        <v>-1.2582</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3986</v>
+        <v>-0.9197</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4455</v>
+        <v>-0.3385</v>
       </c>
       <c r="V11" t="n">
         <v>0.8999</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.8028</v>
+        <v>-11.9104</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2696</v>
+        <v>-1.377000000000001</v>
       </c>
       <c r="F12" t="n">
         <v>-10.5332</v>
@@ -1360,7 +1360,7 @@
         <v>-2.437200000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.0378</v>
+        <v>-4.037799999999999</v>
       </c>
       <c r="J12" t="n">
         <v>1.131899999999999</v>
@@ -1372,7 +1372,7 @@
         <v>-5.8475</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.6071</v>
+        <v>-7.607100000000001</v>
       </c>
       <c r="N12" t="n">
         <v>-9.417</v>
@@ -1390,10 +1390,10 @@
         <v>11.5805</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.0878</v>
+        <v>-5.1954</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.1045</v>
+        <v>-3.2122</v>
       </c>
       <c r="U12" t="n">
         <v>-1.9832</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. VASQUEZ BAUTISTA</t>
+          <t>M. SOLORZANO COLSA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.008800000000001</v>
+        <v>8.3193</v>
       </c>
       <c r="E13" t="n">
-        <v>4.831</v>
+        <v>7.7126</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1778</v>
+        <v>0.6067</v>
       </c>
       <c r="G13" t="n">
-        <v>2.0625</v>
+        <v>5.144</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6831</v>
+        <v>4.6264</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3795</v>
+        <v>0.5177</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9886</v>
+        <v>5.9512</v>
       </c>
       <c r="K13" t="n">
-        <v>1.7851</v>
+        <v>5.9354</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2035</v>
+        <v>0.0157</v>
       </c>
       <c r="M13" t="n">
-        <v>0.07389999999999999</v>
+        <v>-0.8071</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1021</v>
+        <v>-1.3091</v>
       </c>
       <c r="O13" t="n">
-        <v>1.176</v>
+        <v>0.5019</v>
       </c>
       <c r="P13" t="n">
-        <v>0.386</v>
+        <v>-0.193</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3511</v>
+        <v>1.7371</v>
       </c>
       <c r="S13" t="n">
-        <v>2.285</v>
+        <v>1.0351</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0656</v>
+        <v>0.0076</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2195</v>
+        <v>1.0275</v>
       </c>
       <c r="V13" t="n">
-        <v>3.2752</v>
+        <v>2.3331</v>
       </c>
       <c r="W13" t="n">
-        <v>2.7418</v>
+        <v>3.6839</v>
       </c>
       <c r="X13" t="n">
-        <v>0.5334</v>
+        <v>-1.3508</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. SOLORZANO COLSA</t>
+          <t>A. VASQUEZ BAUTISTA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.2571</v>
+        <v>7.3799</v>
       </c>
       <c r="E14" t="n">
-        <v>7.2119</v>
+        <v>4.2301</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0451</v>
+        <v>3.1498</v>
       </c>
       <c r="G14" t="n">
-        <v>5.144</v>
+        <v>2.0625</v>
       </c>
       <c r="H14" t="n">
-        <v>4.6264</v>
+        <v>0.6831</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5177</v>
+        <v>1.3795</v>
       </c>
       <c r="J14" t="n">
-        <v>5.9512</v>
+        <v>1.9886</v>
       </c>
       <c r="K14" t="n">
-        <v>5.9354</v>
+        <v>1.7851</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0157</v>
+        <v>0.2035</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8071</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3091</v>
+        <v>-1.1021</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5019</v>
+        <v>1.176</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7371</v>
+        <v>1.3511</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0271</v>
+        <v>1.6561</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4931</v>
+        <v>0.4647</v>
       </c>
       <c r="U14" t="n">
-        <v>0.466</v>
+        <v>1.1914</v>
       </c>
       <c r="V14" t="n">
-        <v>2.3331</v>
+        <v>3.2752</v>
       </c>
       <c r="W14" t="n">
-        <v>3.6839</v>
+        <v>2.7418</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.3508</v>
+        <v>0.5334</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1222</v>
+        <v>2.334</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5031</v>
+        <v>3.5017</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3809</v>
+        <v>-1.1677</v>
       </c>
       <c r="G15" t="n">
         <v>2.6158</v>
@@ -1624,13 +1624,13 @@
         <v>1.158</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6063</v>
+        <v>1.8181</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7926</v>
+        <v>0.7912</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8136</v>
+        <v>1.0268</v>
       </c>
       <c r="V15" t="n">
         <v>-2.2929</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4553</v>
+        <v>2.1691</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.8516</v>
+        <v>-1.3509</v>
       </c>
       <c r="F16" t="n">
-        <v>3.3068</v>
+        <v>3.52</v>
       </c>
       <c r="G16" t="n">
         <v>1.1479</v>
@@ -1702,13 +1702,13 @@
         <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1143</v>
+        <v>0.8282</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6993</v>
+        <v>-0.1986</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8136</v>
+        <v>1.0268</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5352</v>
+        <v>0.8763</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4697</v>
+        <v>1.1693</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9345</v>
+        <v>-0.293</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6682</v>
@@ -1780,13 +1780,13 @@
         <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3914</v>
+        <v>1.7325</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7232</v>
+        <v>0.4228</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6682</v>
+        <v>1.3097</v>
       </c>
       <c r="V17" t="n">
         <v>0.7771</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1514</v>
+        <v>0.1781</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1514</v>
+        <v>0.1781</v>
       </c>
       <c r="G18" t="n">
         <v>0.1335</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3094</v>
+        <v>-0.7621</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9692</v>
+        <v>-1.769</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6598000000000001</v>
+        <v>1.0069</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8472</v>
@@ -1936,13 +1936,13 @@
         <v>0.579</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2327</v>
+        <v>0.78</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0278</v>
+        <v>0.2281</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2049</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>0.6562</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.4178</v>
+        <v>-5.0215</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6618</v>
+        <v>-2.9608</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7561</v>
+        <v>-2.0607</v>
       </c>
       <c r="G20" t="n">
         <v>-3.1134</v>
@@ -2014,13 +2014,13 @@
         <v>1.7371</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5327</v>
+        <v>0.8636</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4336</v>
+        <v>0.2674</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0992</v>
+        <v>0.5962</v>
       </c>
       <c r="V20" t="n">
         <v>-2.5787</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>12.8028</v>
+        <v>15.4731</v>
       </c>
       <c r="E21" t="n">
-        <v>10.5331</v>
+        <v>10.533</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2694</v>
+        <v>4.9401</v>
       </c>
       <c r="G21" t="n">
         <v>6.4749</v>
@@ -2092,13 +2092,13 @@
         <v>9.650399999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>6.0877</v>
+        <v>8.7582</v>
       </c>
       <c r="T21" t="n">
         <v>1.9832</v>
       </c>
       <c r="U21" t="n">
-        <v>4.1044</v>
+        <v>6.7749</v>
       </c>
       <c r="V21" t="n">
         <v>2.17</v>
